--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.45200866215844</v>
+        <v>10.14845140760075</v>
       </c>
       <c r="D2" t="n">
-        <v>61.7566519370678</v>
+        <v>10.03545593977352</v>
       </c>
       <c r="E2" t="n">
-        <v>1.662079227945205</v>
+        <v>0.2700878745410957</v>
       </c>
       <c r="F2" t="n">
-        <v>1.801223033803903</v>
+        <v>0.2926987429931342</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.54300334756437</v>
+        <v>9.83823804397921</v>
       </c>
       <c r="D3" t="n">
-        <v>61.50387114722611</v>
+        <v>9.994379061424242</v>
       </c>
       <c r="E3" t="n">
-        <v>1.662079227945205</v>
+        <v>0.2700878745410957</v>
       </c>
       <c r="F3" t="n">
-        <v>1.801223033803903</v>
+        <v>0.2926987429931342</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64.61167638419036</v>
+        <v>10.49939741243093</v>
       </c>
       <c r="D4" t="n">
-        <v>65.44495632456285</v>
+        <v>10.63480540274146</v>
       </c>
       <c r="E4" t="n">
-        <v>1.662079227945205</v>
+        <v>0.2700878745410957</v>
       </c>
       <c r="F4" t="n">
-        <v>1.801223033803903</v>
+        <v>0.2926987429931342</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
